--- a/ucsf_n669/cluster_assignments_ucsf_n669_22topics_15clusters_v3.xlsx
+++ b/ucsf_n669/cluster_assignments_ucsf_n669_22topics_15clusters_v3.xlsx
@@ -5,19 +5,20 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bpeng\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bpeng\Documents\pasc_endotyping\github_files\ucsf_n669\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6D7CFB0-E037-49F9-B98E-D02327FFEF92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAC928CF-D847-4D83-86D8-13A33EF74F82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" firstSheet="1" activeTab="3" xr2:uid="{764B6768-4380-4D99-BD04-516190920FD3}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="1" activeTab="2" xr2:uid="{764B6768-4380-4D99-BD04-516190920FD3}"/>
   </bookViews>
   <sheets>
     <sheet name="Cluster_assignments" sheetId="1" r:id="rId1"/>
     <sheet name="Top6_signature_symptoms" sheetId="8" r:id="rId2"/>
     <sheet name="Top3_organ_systems" sheetId="5" r:id="rId3"/>
-    <sheet name="Severity_scores" sheetId="3" r:id="rId4"/>
-    <sheet name="data_dictionary" sheetId="4" r:id="rId5"/>
+    <sheet name="Top3_organ_systems_row" sheetId="9" r:id="rId4"/>
+    <sheet name="Severity_scores" sheetId="3" r:id="rId5"/>
+    <sheet name="data_dictionary" sheetId="4" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -40,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3655" uniqueCount="156">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3703" uniqueCount="176">
   <si>
     <t>Subject_ID</t>
   </si>
@@ -508,6 +509,106 @@
   </si>
   <si>
     <t>Top3_organ_systems</t>
+  </si>
+  <si>
+    <t>['musculo-skeletal', 'sensory changes', 'cognitive/psych']</t>
+  </si>
+  <si>
+    <t>['sexual/hormonal function', 'sensory changes', 'neurological']</t>
+  </si>
+  <si>
+    <t>['neurological', 'musculo-skeletal']</t>
+  </si>
+  <si>
+    <t>['temperature regulation', 'pulmonary', 'g.i']</t>
+  </si>
+  <si>
+    <t>['temperature regulation', 'pulmonary', 'sensory changes']</t>
+  </si>
+  <si>
+    <t>['pulmonary', 'cardiovascular', 'sensory changes']</t>
+  </si>
+  <si>
+    <t>['pulmonary', 'neurological', 'cardiovascular']</t>
+  </si>
+  <si>
+    <t>['musculo-skeletal', 'temperature regulation', 'pulmonary']</t>
+  </si>
+  <si>
+    <t>['sensory changes', 'neurological', 'cognitive/psych']</t>
+  </si>
+  <si>
+    <t>['sensory changes', 'musculo-skeletal', 'g.i']</t>
+  </si>
+  <si>
+    <t>E6</t>
+  </si>
+  <si>
+    <t>E7</t>
+  </si>
+  <si>
+    <t>E8</t>
+  </si>
+  <si>
+    <t>E9</t>
+  </si>
+  <si>
+    <t>E10</t>
+  </si>
+  <si>
+    <t>E11</t>
+  </si>
+  <si>
+    <t>E12</t>
+  </si>
+  <si>
+    <t>E13</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>['sensory changes', 'neurological',</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 'temperature regulation']</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">['sensory changes', 'neurological', </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>'g.i']</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -1063,7 +1164,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1085,14 +1186,13 @@
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="19" fillId="35" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="19" fillId="36" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="19" fillId="37" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="19" fillId="38" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="19" fillId="39" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="19" fillId="34" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1104,6 +1204,9 @@
     <xf numFmtId="0" fontId="20" fillId="40" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1222,22 +1325,88 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>5</xdr:col>
+      <xdr:colOff>49212</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>135046</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>23812</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>143736</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7C47F073-8BB7-E6DF-7836-1CABCB09BCFA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="5835650" y="135046"/>
+          <a:ext cx="3101975" cy="3183690"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
       <xdr:colOff>62016</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>38100</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>412749</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>195153</xdr:rowOff>
+      <xdr:colOff>408939</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>525</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="Picture 3">
+        <xdr:cNvPr id="2" name="Picture 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2BF523AD-34A0-2115-0E59-3F137FC266C5}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DEF9D99A-DDC2-4BFA-B2F8-C770B9A78802}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1259,8 +1428,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5853216" y="38100"/>
-          <a:ext cx="2865333" cy="3306653"/>
+          <a:off x="5849406" y="38100"/>
+          <a:ext cx="2867238" cy="3359358"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1272,7 +1441,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -19090,7 +19259,7 @@
   <dimension ref="A1:P7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="17.44140625" style="17" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.44140625" style="16" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="7.109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="5.88671875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="5.5546875" bestFit="1" customWidth="1"/>
@@ -19103,58 +19272,58 @@
     <col min="15" max="16" width="7" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="16" t="s">
+    <row r="1" spans="1:16" s="16" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="15" t="s">
         <v>47</v>
       </c>
-      <c r="B1" s="17" t="s">
+      <c r="B1" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="C1" s="17" t="s">
+      <c r="C1" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="D1" s="17" t="s">
+      <c r="D1" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="E1" s="17" t="s">
+      <c r="E1" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="F1" s="17" t="s">
+      <c r="F1" s="16" t="s">
         <v>52</v>
       </c>
-      <c r="G1" s="17" t="s">
+      <c r="G1" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="H1" s="17" t="s">
+      <c r="H1" s="16" t="s">
         <v>54</v>
       </c>
-      <c r="I1" s="17" t="s">
+      <c r="I1" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="J1" s="17" t="s">
+      <c r="J1" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="K1" s="17" t="s">
+      <c r="K1" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="L1" s="17" t="s">
+      <c r="L1" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="M1" s="17" t="s">
+      <c r="M1" s="16" t="s">
         <v>59</v>
       </c>
-      <c r="N1" s="17" t="s">
+      <c r="N1" s="16" t="s">
         <v>60</v>
       </c>
-      <c r="O1" s="17" t="s">
+      <c r="O1" s="16" t="s">
         <v>61</v>
       </c>
-      <c r="P1" s="17" t="s">
+      <c r="P1" s="16" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A2" s="17" t="s">
+      <c r="A2" s="16" t="s">
         <v>63</v>
       </c>
       <c r="B2" t="s">
@@ -19204,7 +19373,7 @@
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A3" s="17" t="s">
+      <c r="A3" s="16" t="s">
         <v>77</v>
       </c>
       <c r="B3" t="s">
@@ -19254,7 +19423,7 @@
       </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A4" s="17" t="s">
+      <c r="A4" s="16" t="s">
         <v>86</v>
       </c>
       <c r="B4" t="s">
@@ -19304,7 +19473,7 @@
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A5" s="17" t="s">
+      <c r="A5" s="16" t="s">
         <v>94</v>
       </c>
       <c r="B5" t="s">
@@ -19354,7 +19523,7 @@
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A6" s="18" t="s">
+      <c r="A6" s="17" t="s">
         <v>98</v>
       </c>
       <c r="B6" t="s">
@@ -19404,7 +19573,7 @@
       </c>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A7" s="17" t="s">
+      <c r="A7" s="16" t="s">
         <v>100</v>
       </c>
       <c r="B7" t="s">
@@ -19480,257 +19649,206 @@
       <c r="B1" s="8" t="s">
         <v>154</v>
       </c>
-      <c r="C1" s="9" t="s">
-        <v>145</v>
-      </c>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
+      <c r="C1" s="19" t="s">
+        <v>155</v>
+      </c>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="20" t="s">
+        <v>56</v>
+      </c>
+      <c r="B2" s="20" t="s">
+        <v>167</v>
+      </c>
+      <c r="C2" s="20" t="s">
+        <v>32</v>
+      </c>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="20" t="s">
+        <v>59</v>
+      </c>
+      <c r="B3" s="20" t="s">
+        <v>170</v>
+      </c>
+      <c r="C3" s="20" t="s">
+        <v>156</v>
+      </c>
+      <c r="D3" s="20"/>
+      <c r="E3" s="20"/>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="C4" s="20" t="s">
+        <v>157</v>
+      </c>
+      <c r="D4" s="20"/>
+      <c r="E4" s="20"/>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="20" t="s">
         <v>58</v>
       </c>
-      <c r="B2" s="15" t="s">
+      <c r="B5" s="20" t="s">
+        <v>169</v>
+      </c>
+      <c r="C5" s="20" t="s">
+        <v>158</v>
+      </c>
+      <c r="D5" s="20"/>
+      <c r="E5" s="20"/>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="20" t="s">
+        <v>50</v>
+      </c>
+      <c r="B6" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" s="20" t="s">
+        <v>174</v>
+      </c>
+      <c r="D6" s="20"/>
+      <c r="E6" s="20"/>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="B7" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="20" t="s">
+        <v>175</v>
+      </c>
+      <c r="D7" s="20"/>
+      <c r="E7" s="21"/>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8" s="20" t="s">
+        <v>60</v>
+      </c>
+      <c r="B8" s="20" t="s">
+        <v>171</v>
+      </c>
+      <c r="C8" s="20" t="s">
+        <v>159</v>
+      </c>
+      <c r="D8" s="20"/>
+      <c r="E8" s="20"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" s="20" t="s">
+        <v>49</v>
+      </c>
+      <c r="B9" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="C9" s="20" t="s">
+        <v>160</v>
+      </c>
+      <c r="D9" s="20"/>
+      <c r="E9" s="20"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10" s="20" t="s">
+        <v>54</v>
+      </c>
+      <c r="B10" s="20" t="s">
+        <v>166</v>
+      </c>
+      <c r="C10" s="20" t="s">
+        <v>161</v>
+      </c>
+      <c r="D10" s="20"/>
+      <c r="E10" s="20"/>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="B11" s="20" t="s">
+        <v>168</v>
+      </c>
+      <c r="C11" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="D11" s="20"/>
+      <c r="E11" s="20"/>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A12" s="20" t="s">
+        <v>52</v>
+      </c>
+      <c r="B12" s="20" t="s">
         <v>35</v>
       </c>
-      <c r="C2" s="7" t="s">
-        <v>144</v>
-      </c>
-      <c r="D2" s="7" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="B3" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="C3" s="7" t="s">
-        <v>146</v>
-      </c>
-      <c r="D3" s="7" t="s">
-        <v>147</v>
-      </c>
-      <c r="E3" s="7" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="B4" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="C4" s="7" t="s">
-        <v>146</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>147</v>
-      </c>
-      <c r="E4" s="7" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="B5" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="C5" s="7" t="s">
-        <v>150</v>
-      </c>
-      <c r="D5" s="7" t="s">
-        <v>146</v>
-      </c>
-      <c r="E5" s="7" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="B6" s="14" t="s">
+      <c r="C12" s="20" t="s">
+        <v>162</v>
+      </c>
+      <c r="D12" s="20"/>
+      <c r="E12" s="20"/>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A13" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="B13" s="20" t="s">
+        <v>8</v>
+      </c>
+      <c r="C13" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="D13" s="20"/>
+      <c r="E13" s="20"/>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A14" s="20" t="s">
+        <v>51</v>
+      </c>
+      <c r="B14" s="20" t="s">
         <v>30</v>
       </c>
-      <c r="C6" s="7" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="B7" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>150</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>151</v>
-      </c>
-      <c r="E7" s="7" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A8" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="B8" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="C8" s="7" t="s">
-        <v>144</v>
-      </c>
-      <c r="D8" s="7" t="s">
-        <v>151</v>
-      </c>
-      <c r="E8" s="7" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="B9" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="C9" s="7" t="s">
-        <v>152</v>
-      </c>
-      <c r="D9" s="7" t="s">
-        <v>144</v>
-      </c>
-      <c r="E9" s="7" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A10" s="7" t="s">
+      <c r="C14" s="20" t="s">
+        <v>163</v>
+      </c>
+      <c r="D14" s="20"/>
+      <c r="E14" s="20"/>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" s="20" t="s">
         <v>61</v>
       </c>
-      <c r="B10" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="C10" s="7" t="s">
-        <v>152</v>
-      </c>
-      <c r="D10" s="7" t="s">
-        <v>146</v>
-      </c>
-      <c r="E10" s="7" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11" s="7" t="s">
+      <c r="B15" s="20" t="s">
+        <v>172</v>
+      </c>
+      <c r="C15" s="20" t="s">
+        <v>164</v>
+      </c>
+      <c r="D15" s="20"/>
+      <c r="E15" s="20"/>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16" s="20" t="s">
         <v>62</v>
       </c>
-      <c r="B11" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="C11" s="7" t="s">
-        <v>150</v>
-      </c>
-      <c r="D11" s="7" t="s">
-        <v>144</v>
-      </c>
-      <c r="E11" s="7" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A12" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="B12" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="C12" s="7" t="s">
-        <v>153</v>
-      </c>
-      <c r="D12" s="7" t="s">
-        <v>150</v>
-      </c>
-      <c r="E12" s="7" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A13" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="B13" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="C13" s="7" t="s">
-        <v>153</v>
-      </c>
-      <c r="D13" s="7" t="s">
-        <v>146</v>
-      </c>
-      <c r="E13" s="7" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A14" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="B14" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="C14" s="7" t="s">
-        <v>144</v>
-      </c>
-      <c r="D14" s="7" t="s">
-        <v>151</v>
-      </c>
-      <c r="E14" s="7" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A15" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="B15" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="C15" s="7" t="s">
-        <v>151</v>
-      </c>
-      <c r="D15" s="7" t="s">
-        <v>147</v>
-      </c>
-      <c r="E15" s="7" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A16" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="B16" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="C16" s="7" t="s">
-        <v>153</v>
-      </c>
-      <c r="D16" s="7" t="s">
-        <v>151</v>
-      </c>
-      <c r="E16" s="7" t="s">
-        <v>147</v>
-      </c>
+      <c r="B16" s="20" t="s">
+        <v>173</v>
+      </c>
+      <c r="C16" s="20" t="s">
+        <v>165</v>
+      </c>
+      <c r="D16" s="20"/>
+      <c r="E16" s="20"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -19742,6 +19860,288 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9EFA230F-DF04-41DD-B1B0-3ACFD7A83740}">
+  <dimension ref="A1:E16"/>
+  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="10.6640625" style="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.5546875" style="7" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.44140625" style="7" customWidth="1"/>
+    <col min="4" max="4" width="16.6640625" style="7" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="24.109375" style="7" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10" style="7" customWidth="1"/>
+    <col min="7" max="16384" width="8.88671875" style="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" s="8" customFormat="1" ht="31.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>154</v>
+      </c>
+      <c r="C1" s="19" t="s">
+        <v>145</v>
+      </c>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="B2" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="B3" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="B5" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="B6" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="B7" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="B9" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="B10" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="B11" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A12" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="B12" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>153</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A13" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="B13" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>153</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A14" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="B14" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="E14" s="7" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="B15" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="E15" s="7" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="B16" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>153</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="E16" s="7" t="s">
+        <v>147</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="C1:E1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D71A152-B7EC-4C2E-AB66-3969A9F847F1}">
   <dimension ref="A1:D16"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -19776,7 +20176,7 @@
       <c r="C2" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="D2" s="19" t="s">
+      <c r="D2" s="18" t="s">
         <v>105</v>
       </c>
     </row>
@@ -19982,7 +20382,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36DC8496-39C1-4E42-BC93-BB8FE1FADEEB}">
   <dimension ref="A1:B33"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
